--- a/assets/templates/花名册模板.xlsx
+++ b/assets/templates/花名册模板.xlsx
@@ -426,17 +426,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -447,35 +448,40 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>学籍号</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>性别</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>小组</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>排</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>列</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>班委职务</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>家长姓名</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>联系电话</t>
         </is>
@@ -489,35 +495,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>20260001</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>男</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>班长</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>张某某</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>13800000000</t>
         </is>
